--- a/XLibur.Tests/Resource/Other/Charts/PreserveCharts/outputfile.xlsx
+++ b/XLibur.Tests/Resource/Other/Charts/PreserveCharts/outputfile.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Date</x:t>
   </x:si>
